--- a/sheet/money-rooms-blank.xlsx
+++ b/sheet/money-rooms-blank.xlsx
@@ -7502,9 +7502,6 @@
           <t xml:space="preserve">Net worth, weighted by how sure you are</t>
         </is>
       </c>
-      <c r="C64" s="18">
-        <f>SUM(assetValue)-totalDebt</f>
-      </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">dollars</t>
